--- a/Справочник команд.xlsx
+++ b/Справочник команд.xlsx
@@ -5,16 +5,17 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\iudintsev\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PRACTICUM\handbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="31500" windowHeight="17475" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="31500" windowHeight="17475" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Docker commands" sheetId="1" r:id="rId1"/>
     <sheet name="Server commands" sheetId="2" r:id="rId2"/>
     <sheet name="Git" sheetId="3" r:id="rId3"/>
+    <sheet name="pip" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="55">
   <si>
     <t>Команда</t>
   </si>
@@ -324,6 +325,57 @@
   </si>
   <si>
     <t>Переместить папку/файл с подтвеждением.</t>
+  </si>
+  <si>
+    <t>git branch название_ветки</t>
+  </si>
+  <si>
+    <t>Создание новой ветки.</t>
+  </si>
+  <si>
+    <t>git checkout название ветки</t>
+  </si>
+  <si>
+    <t>Переключение на другую ветку.</t>
+  </si>
+  <si>
+    <t>git checkout -b develop</t>
+  </si>
+  <si>
+    <t>Создать ветку и сразу переключиться на неё.</t>
+  </si>
+  <si>
+    <t>pip install -r requirements.txt</t>
+  </si>
+  <si>
+    <t>Установить пакеты перечисленные в requirements.txt</t>
+  </si>
+  <si>
+    <t>pip freeze &gt; requirements.txt</t>
+  </si>
+  <si>
+    <t>Завиксировать в файле доустановленные пакеты.</t>
+  </si>
+  <si>
+    <t>pip install -r requirements.txt --upgrade --force-reinstall</t>
+  </si>
+  <si>
+    <t>Установить всё заново. Переустанавливает все пакеты из файла.</t>
+  </si>
+  <si>
+    <t>Доустановить недостающие. Устанавливает только новые/изменённые.</t>
+  </si>
+  <si>
+    <t>pip-sync requirements.txt</t>
+  </si>
+  <si>
+    <t>Удалить лишние. Приводит окружение в точное соответствие с файлом.</t>
+  </si>
+  <si>
+    <t>rm -rf venv &amp;&amp; python -m venv venv &amp;&amp; pip install -r requirements.txt</t>
+  </si>
+  <si>
+    <t>Очистка и переустановка. Полная переустановка в чистом окружении.</t>
   </si>
 </sst>
 </file>
@@ -845,7 +897,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32.85546875" customWidth="1"/>
@@ -932,6 +984,101 @@
         <v>32</v>
       </c>
     </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="63.85546875" customWidth="1"/>
+    <col min="2" max="2" width="67.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B6" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B7" t="s">
+        <v>54</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>

--- a/Справочник команд.xlsx
+++ b/Справочник команд.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="31500" windowHeight="17475" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="31500" windowHeight="17475" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Docker commands" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="86">
   <si>
     <t>Команда</t>
   </si>
@@ -376,13 +376,316 @@
   </si>
   <si>
     <t>Очистка и переустановка. Полная переустановка в чистом окружении.</t>
+  </si>
+  <si>
+    <t>docker build -t &lt;имя_образа&gt; .</t>
+  </si>
+  <si>
+    <t>Собрать/пересобрать образ.</t>
+  </si>
+  <si>
+    <t>docker compose up</t>
+  </si>
+  <si>
+    <t>Поднимает сеть из контейнеров.</t>
+  </si>
+  <si>
+    <t>Удаляет работающую сеть и контейнеры.</t>
+  </si>
+  <si>
+    <t>docker compose exec backend python manage.py migrate</t>
+  </si>
+  <si>
+    <t>docker compose stop &amp;&amp; docker compose up --build</t>
+  </si>
+  <si>
+    <t>Команды, объединённые символами &amp;&amp;, выполняются последовательно; вторая команда выполнится, только если первая выполнилась успешно. Ключ --build для docker compose up означает, что перед запуском нужно пересобрать образы.</t>
+  </si>
+  <si>
+    <t>git merge develop</t>
+  </si>
+  <si>
+    <t>Влить в текущую ветку данные из ветки develop.</t>
+  </si>
+  <si>
+    <t>git pull origin</t>
+  </si>
+  <si>
+    <t>Влить изменения из всех веток удалённого репозитория в соответствующие локальные ветки.</t>
+  </si>
+  <si>
+    <t>git branch -d &lt;ветка&gt;</t>
+  </si>
+  <si>
+    <t>git branc -D &lt;ветка&gt;</t>
+  </si>
+  <si>
+    <t>Удаление ветки.</t>
+  </si>
+  <si>
+    <t>Принудительное удаление ветки.</t>
+  </si>
+  <si>
+    <t>git push origin --delete имя-ветки</t>
+  </si>
+  <si>
+    <t>Удаление ветки на Github.</t>
+  </si>
+  <si>
+    <r>
+      <t>docker</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> rmi </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF4078F2"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>&lt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>image_id</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF4078F2"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>&gt;</t>
+    </r>
+  </si>
+  <si>
+    <t>Удалить образ.</t>
+  </si>
+  <si>
+    <t>Удалить остановленные контейнеры.</t>
+  </si>
+  <si>
+    <r>
+      <t>sudo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4078F2"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>docker</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> image prune </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4078F2"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>-f</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>sudo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4078F2"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>docker</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> container prune </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4078F2"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>-f</t>
+    </r>
+  </si>
+  <si>
+    <t>Удалить неиспользуемые образы.</t>
+  </si>
+  <si>
+    <r>
+      <t>sudo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4078F2"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>docker</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> network prune </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4078F2"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>-f</t>
+    </r>
+  </si>
+  <si>
+    <t>Удалить неиспользуемые сети.</t>
+  </si>
+  <si>
+    <t>Блок по очистке сервера</t>
+  </si>
+  <si>
+    <r>
+      <t>sudo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4078F2"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>docker</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> builder prune </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4078F2"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>-af</t>
+    </r>
+  </si>
+  <si>
+    <t>Удалить build cache.</t>
+  </si>
+  <si>
+    <t>df -h</t>
+  </si>
+  <si>
+    <t>Посмотреть сколько места всего свободного/занятого.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -451,6 +754,35 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0F1115"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF4078F2"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF4078F2"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF4078F2"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+      <charset val="204"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -472,7 +804,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -486,9 +818,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -500,6 +829,12 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -780,10 +1115,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="50.85546875" customWidth="1"/>
+    <col min="1" max="1" width="75.140625" customWidth="1"/>
     <col min="2" max="2" width="61.5703125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -820,19 +1155,101 @@
       </c>
     </row>
     <row r="5" spans="1:2" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+    <row r="6" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="60" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="11" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -843,7 +1260,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
@@ -859,35 +1276,43 @@
       </c>
     </row>
     <row r="2" spans="1:2" ht="44.25" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="44.25" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="5" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="5" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="5" t="s">
         <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -897,10 +1322,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="32.85546875" customWidth="1"/>
+    <col min="1" max="1" width="36.5703125" customWidth="1"/>
     <col min="2" max="2" width="57.5703125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -916,7 +1341,7 @@
       <c r="A2" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="8" t="s">
         <v>35</v>
       </c>
     </row>
@@ -953,59 +1378,99 @@
       </c>
     </row>
     <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B8" s="5" t="s">
         <v>27</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>28</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>31</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>30</v>
+        <v>28</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>33</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>38</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>39</v>
+        <v>33</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>40</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>41</v>
+        <v>38</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B14" s="7" t="s">
         <v>43</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>63</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>67</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>68</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>71</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>
